--- a/generation_zy/sowo-物料1.xlsx
+++ b/generation_zy/sowo-物料1.xlsx
@@ -482,7 +482,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260710-001</t>
+          <t>20260920-001</t>
         </is>
       </c>
       <c r="B7" t="n">
